--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-20.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-20.xlsx
@@ -1789,7 +1789,7 @@
     <t>Cesar Vallejo Moquegua</t>
   </si>
   <si>
-    <t>2026-09-18 02:08:29</t>
+    <t>2026-09-18 04:43:13</t>
   </si>
 </sst>
 </file>
@@ -2383,7 +2383,7 @@
         <v>392</v>
       </c>
       <c r="F2">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="G2">
         <v>1.96</v>
@@ -2392,13 +2392,13 @@
         <v>4.5</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L2">
         <v>1.46</v>
@@ -2413,7 +2413,7 @@
         <v>1.38</v>
       </c>
       <c r="P2">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q2">
         <v>2.08</v>
@@ -2431,13 +2431,13 @@
         <v>1.96</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W2">
         <v>2.04</v>
       </c>
       <c r="X2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y2">
         <v>15</v>
@@ -2485,7 +2485,7 @@
         <v>160</v>
       </c>
       <c r="AN2">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AO2">
         <v>110</v>
@@ -2497,10 +2497,10 @@
         <v>13</v>
       </c>
       <c r="AR2">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AS2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2">
         <v>7</v>
@@ -2509,10 +2509,10 @@
         <v>7.4</v>
       </c>
       <c r="AV2">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AX2">
         <v>9.800000000000001</v>
@@ -2524,25 +2524,25 @@
         <v>17.5</v>
       </c>
       <c r="BA2">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC2">
         <v>17.5</v>
       </c>
       <c r="BD2">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH2">
         <v>3.5</v>
@@ -2631,16 +2631,16 @@
         <v>4</v>
       </c>
       <c r="H3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I3">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -2673,7 +2673,7 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="W3">
         <v>1.33</v>
@@ -2867,22 +2867,22 @@
         <v>394</v>
       </c>
       <c r="F4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G4">
         <v>2.1</v>
       </c>
       <c r="H4">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I4">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2897,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="P4">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
@@ -3112,7 +3112,7 @@
         <v>1.98</v>
       </c>
       <c r="G5">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H5">
         <v>4.8</v>
@@ -3124,13 +3124,13 @@
         <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L5">
         <v>1.52</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5">
         <v>2.58</v>
@@ -3148,31 +3148,31 @@
         <v>1.15</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T5">
         <v>2.1</v>
       </c>
       <c r="U5">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="V5">
         <v>1.24</v>
       </c>
       <c r="W5">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X5">
         <v>8.800000000000001</v>
       </c>
       <c r="Y5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z5">
         <v>44</v>
       </c>
       <c r="AA5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB5">
         <v>6.6</v>
@@ -3193,13 +3193,13 @@
         <v>12</v>
       </c>
       <c r="AH5">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI5">
         <v>140</v>
       </c>
       <c r="AJ5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK5">
         <v>32</v>
@@ -3214,64 +3214,64 @@
         <v>32</v>
       </c>
       <c r="AO5">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP5">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ5">
         <v>10.5</v>
       </c>
       <c r="AR5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS5">
         <v>100</v>
       </c>
       <c r="AT5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU5">
         <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW5">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY5">
         <v>10</v>
       </c>
       <c r="AZ5">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BB5">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BD5">
         <v>42</v>
       </c>
       <c r="BE5">
-        <v>150</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BG5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BH5">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI5">
         <v>2.34</v>
@@ -3289,7 +3289,7 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO5">
         <v>3.6</v>
@@ -3357,10 +3357,10 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I6">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="J6">
         <v>4.5</v>
@@ -3372,7 +3372,7 @@
         <v>1.24</v>
       </c>
       <c r="M6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N6">
         <v>6.8</v>
@@ -3381,7 +3381,7 @@
         <v>1.15</v>
       </c>
       <c r="P6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q6">
         <v>1.47</v>
@@ -3390,16 +3390,16 @@
         <v>1.8</v>
       </c>
       <c r="S6">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="T6">
         <v>1.5</v>
       </c>
       <c r="U6">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="V6">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="W6">
         <v>1.25</v>
@@ -3459,58 +3459,58 @@
         <v>7.2</v>
       </c>
       <c r="AP6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="AQ6">
+        <v>11.5</v>
+      </c>
+      <c r="AR6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS6">
         <v>12</v>
       </c>
-      <c r="AR6">
-        <v>11</v>
-      </c>
-      <c r="AS6">
-        <v>2.68</v>
-      </c>
       <c r="AT6">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AU6">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW6">
         <v>12</v>
       </c>
       <c r="AX6">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="AY6">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AZ6">
         <v>12</v>
       </c>
       <c r="BA6">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BB6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BC6">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BD6">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BE6">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BF6">
         <v>18.5</v>
       </c>
       <c r="BG6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -3593,22 +3593,22 @@
         <v>397</v>
       </c>
       <c r="F7">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G7">
         <v>1.78</v>
       </c>
       <c r="H7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I7">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>4.3</v>
       </c>
       <c r="K7">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L7">
         <v>1.29</v>
@@ -3626,13 +3626,13 @@
         <v>2.58</v>
       </c>
       <c r="Q7">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R7">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S7">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T7">
         <v>1.56</v>
@@ -3683,7 +3683,7 @@
         <v>70</v>
       </c>
       <c r="AJ7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK7">
         <v>23</v>
@@ -3695,7 +3695,7 @@
         <v>95</v>
       </c>
       <c r="AN7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO7">
         <v>60</v>
@@ -3713,43 +3713,43 @@
         <v>3.5</v>
       </c>
       <c r="AT7">
-        <v>2.84</v>
+        <v>10.5</v>
       </c>
       <c r="AU7">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AV7">
         <v>3.1</v>
       </c>
       <c r="AW7">
+        <v>3.3</v>
+      </c>
+      <c r="AX7">
+        <v>2.86</v>
+      </c>
+      <c r="AY7">
+        <v>9</v>
+      </c>
+      <c r="AZ7">
+        <v>3.05</v>
+      </c>
+      <c r="BA7">
+        <v>3.3</v>
+      </c>
+      <c r="BB7">
+        <v>3.1</v>
+      </c>
+      <c r="BC7">
+        <v>10</v>
+      </c>
+      <c r="BD7">
+        <v>3.15</v>
+      </c>
+      <c r="BE7">
         <v>3.35</v>
       </c>
-      <c r="AX7">
-        <v>2.88</v>
-      </c>
-      <c r="AY7">
-        <v>7.4</v>
-      </c>
-      <c r="AZ7">
-        <v>13</v>
-      </c>
-      <c r="BA7">
-        <v>3.35</v>
-      </c>
-      <c r="BB7">
-        <v>14</v>
-      </c>
-      <c r="BC7">
-        <v>12</v>
-      </c>
-      <c r="BD7">
-        <v>18.5</v>
-      </c>
-      <c r="BE7">
-        <v>3.4</v>
-      </c>
       <c r="BF7">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG7">
         <v>3.3</v>
@@ -3835,16 +3835,16 @@
         <v>398</v>
       </c>
       <c r="F8">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G8">
         <v>1.75</v>
       </c>
       <c r="H8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>4.6</v>
@@ -3853,7 +3853,7 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M8">
         <v>1.03</v>
@@ -3871,16 +3871,16 @@
         <v>1.5</v>
       </c>
       <c r="R8">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S8">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T8">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="U8">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="V8">
         <v>1.25</v>
@@ -3889,112 +3889,112 @@
         <v>2.32</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA8">
         <v>1000</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC8">
+        <v>12.5</v>
+      </c>
+      <c r="AD8">
+        <v>25</v>
+      </c>
+      <c r="AE8">
+        <v>170</v>
+      </c>
+      <c r="AF8">
+        <v>16</v>
+      </c>
+      <c r="AG8">
+        <v>12</v>
+      </c>
+      <c r="AH8">
+        <v>20</v>
+      </c>
+      <c r="AI8">
+        <v>120</v>
+      </c>
+      <c r="AJ8">
+        <v>25</v>
+      </c>
+      <c r="AK8">
+        <v>18</v>
+      </c>
+      <c r="AL8">
+        <v>36</v>
+      </c>
+      <c r="AM8">
+        <v>470</v>
+      </c>
+      <c r="AN8">
+        <v>6.6</v>
+      </c>
+      <c r="AO8">
+        <v>75</v>
+      </c>
+      <c r="AP8">
+        <v>21</v>
+      </c>
+      <c r="AQ8">
+        <v>18</v>
+      </c>
+      <c r="AR8">
+        <v>25</v>
+      </c>
+      <c r="AS8">
+        <v>3.9</v>
+      </c>
+      <c r="AT8">
+        <v>11.5</v>
+      </c>
+      <c r="AU8">
+        <v>9</v>
+      </c>
+      <c r="AV8">
+        <v>14</v>
+      </c>
+      <c r="AW8">
+        <v>26</v>
+      </c>
+      <c r="AX8">
+        <v>11</v>
+      </c>
+      <c r="AY8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8">
+        <v>12.5</v>
+      </c>
+      <c r="BA8">
+        <v>25</v>
+      </c>
+      <c r="BB8">
+        <v>14.5</v>
+      </c>
+      <c r="BC8">
+        <v>11.5</v>
+      </c>
+      <c r="BD8">
+        <v>17</v>
+      </c>
+      <c r="BE8">
+        <v>3.9</v>
+      </c>
+      <c r="BF8">
+        <v>5.7</v>
+      </c>
+      <c r="BG8">
         <v>22</v>
-      </c>
-      <c r="AD8">
-        <v>1000</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>34</v>
-      </c>
-      <c r="AG8">
-        <v>19.5</v>
-      </c>
-      <c r="AH8">
-        <v>1000</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>8.4</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>1.32</v>
-      </c>
-      <c r="AQ8">
-        <v>1.32</v>
-      </c>
-      <c r="AR8">
-        <v>1.32</v>
-      </c>
-      <c r="AS8">
-        <v>1.32</v>
-      </c>
-      <c r="AT8">
-        <v>9.4</v>
-      </c>
-      <c r="AU8">
-        <v>7.8</v>
-      </c>
-      <c r="AV8">
-        <v>1.32</v>
-      </c>
-      <c r="AW8">
-        <v>1.32</v>
-      </c>
-      <c r="AX8">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY8">
-        <v>7.4</v>
-      </c>
-      <c r="AZ8">
-        <v>1.32</v>
-      </c>
-      <c r="BA8">
-        <v>1.32</v>
-      </c>
-      <c r="BB8">
-        <v>1.32</v>
-      </c>
-      <c r="BC8">
-        <v>9.6</v>
-      </c>
-      <c r="BD8">
-        <v>1.32</v>
-      </c>
-      <c r="BE8">
-        <v>1.32</v>
-      </c>
-      <c r="BF8">
-        <v>4.9</v>
-      </c>
-      <c r="BG8">
-        <v>1.32</v>
       </c>
       <c r="BH8">
         <v>5.7</v>
@@ -4080,7 +4080,7 @@
         <v>1.93</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H9">
         <v>3.8</v>
@@ -4089,7 +4089,7 @@
         <v>4.1</v>
       </c>
       <c r="J9">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K9">
         <v>4.4</v>
@@ -4110,19 +4110,19 @@
         <v>2.6</v>
       </c>
       <c r="Q9">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R9">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S9">
         <v>2.46</v>
       </c>
       <c r="T9">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U9">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="V9">
         <v>1.32</v>
@@ -4143,7 +4143,7 @@
         <v>100</v>
       </c>
       <c r="AB9">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC9">
         <v>10.5</v>
@@ -4152,7 +4152,7 @@
         <v>16.5</v>
       </c>
       <c r="AE9">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF9">
         <v>15.5</v>
@@ -4185,16 +4185,16 @@
         <v>32</v>
       </c>
       <c r="AP9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AR9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT9">
         <v>12</v>
@@ -4206,7 +4206,7 @@
         <v>14.5</v>
       </c>
       <c r="AW9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX9">
         <v>13</v>
@@ -4218,7 +4218,7 @@
         <v>14</v>
       </c>
       <c r="BA9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB9">
         <v>20</v>
@@ -4227,16 +4227,16 @@
         <v>16</v>
       </c>
       <c r="BD9">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9">
         <v>5</v>
@@ -4266,7 +4266,7 @@
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR9">
         <v>1000</v>
@@ -4319,7 +4319,7 @@
         <v>400</v>
       </c>
       <c r="F10">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G10">
         <v>1.74</v>
@@ -4328,7 +4328,7 @@
         <v>4.8</v>
       </c>
       <c r="I10">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J10">
         <v>4.4</v>
@@ -4349,13 +4349,13 @@
         <v>1.17</v>
       </c>
       <c r="P10">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q10">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="R10">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S10">
         <v>2.3</v>
@@ -4373,7 +4373,7 @@
         <v>2.32</v>
       </c>
       <c r="X10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
         <v>1000</v>
@@ -4403,7 +4403,7 @@
         <v>20</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AI10">
         <v>1000</v>
@@ -4427,16 +4427,16 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>24</v>
+        <v>1.42</v>
       </c>
       <c r="AQ10">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AR10">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AS10">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AT10">
         <v>9.199999999999999</v>
@@ -4448,7 +4448,7 @@
         <v>11.5</v>
       </c>
       <c r="AW10">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AX10">
         <v>9</v>
@@ -4460,7 +4460,7 @@
         <v>10.5</v>
       </c>
       <c r="BA10">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BB10">
         <v>11</v>
@@ -4469,16 +4469,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD10">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BE10">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BF10">
         <v>5</v>
       </c>
       <c r="BG10">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BH10">
         <v>5.5</v>
@@ -4561,22 +4561,22 @@
         <v>401</v>
       </c>
       <c r="F11">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="G11">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="H11">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="I11">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="J11">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
         <v>1.26</v>
@@ -4585,46 +4585,46 @@
         <v>1.04</v>
       </c>
       <c r="N11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
         <v>1.21</v>
       </c>
       <c r="P11">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="Q11">
         <v>1.64</v>
       </c>
       <c r="R11">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S11">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T11">
         <v>1.57</v>
       </c>
       <c r="U11">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="V11">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W11">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X11">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z11">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA11">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AB11">
         <v>15.5</v>
@@ -4636,10 +4636,10 @@
         <v>13</v>
       </c>
       <c r="AE11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF11">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG11">
         <v>13</v>
@@ -4654,7 +4654,7 @@
         <v>38</v>
       </c>
       <c r="AK11">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL11">
         <v>32</v>
@@ -4663,10 +4663,10 @@
         <v>70</v>
       </c>
       <c r="AN11">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AO11">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AP11">
         <v>8</v>
@@ -4675,7 +4675,7 @@
         <v>14</v>
       </c>
       <c r="AR11">
-        <v>17.5</v>
+        <v>8</v>
       </c>
       <c r="AS11">
         <v>32</v>
@@ -4690,10 +4690,10 @@
         <v>11.5</v>
       </c>
       <c r="AW11">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX11">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY11">
         <v>11</v>
@@ -4702,22 +4702,22 @@
         <v>13</v>
       </c>
       <c r="BA11">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB11">
-        <v>32</v>
+        <v>9.6</v>
       </c>
       <c r="BC11">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD11">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG11">
         <v>14</v>
@@ -4744,7 +4744,7 @@
         <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BP11">
         <v>1000</v>
@@ -4762,7 +4762,7 @@
         <v>1000</v>
       </c>
       <c r="BU11">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV11">
         <v>1000</v>
@@ -4803,7 +4803,7 @@
         <v>402</v>
       </c>
       <c r="F12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G12">
         <v>1.55</v>
@@ -4815,10 +4815,10 @@
         <v>110</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -4830,19 +4830,19 @@
         <v>3.5</v>
       </c>
       <c r="O12">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P12">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="Q12">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="R12">
         <v>1.35</v>
       </c>
       <c r="S12">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -5048,16 +5048,16 @@
         <v>3</v>
       </c>
       <c r="G13">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H13">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="I13">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="J13">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="K13">
         <v>930</v>
@@ -5084,7 +5084,7 @@
         <v>1.28</v>
       </c>
       <c r="S13">
-        <v>3.5</v>
+        <v>2.02</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -5093,10 +5093,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -5317,22 +5317,22 @@
         <v>1.25</v>
       </c>
       <c r="P14">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q14">
         <v>1.78</v>
       </c>
       <c r="R14">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S14">
         <v>3</v>
       </c>
       <c r="T14">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U14">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="V14">
         <v>1.31</v>
@@ -5341,49 +5341,49 @@
         <v>2.02</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA14">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
         <v>11</v>
       </c>
       <c r="AC14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD14">
+        <v>21</v>
+      </c>
+      <c r="AE14">
+        <v>110</v>
+      </c>
+      <c r="AF14">
         <v>15</v>
-      </c>
-      <c r="AD14">
-        <v>1000</v>
-      </c>
-      <c r="AE14">
-        <v>1000</v>
-      </c>
-      <c r="AF14">
-        <v>28</v>
       </c>
       <c r="AG14">
         <v>11</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM14">
         <v>1000</v>
@@ -5392,61 +5392,61 @@
         <v>11.5</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP14">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AQ14">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AR14">
-        <v>1.61</v>
+        <v>19.5</v>
       </c>
       <c r="AS14">
-        <v>1.59</v>
+        <v>4.2</v>
       </c>
       <c r="AT14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU14">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AW14">
-        <v>1.61</v>
+        <v>25</v>
       </c>
       <c r="AX14">
         <v>11</v>
       </c>
       <c r="AY14">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA14">
-        <v>1.61</v>
+        <v>27</v>
       </c>
       <c r="BB14">
-        <v>1.61</v>
+        <v>16</v>
       </c>
       <c r="BC14">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BD14">
-        <v>1.61</v>
+        <v>20</v>
       </c>
       <c r="BE14">
-        <v>1.61</v>
+        <v>4.4</v>
       </c>
       <c r="BF14">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG14">
-        <v>1.61</v>
+        <v>4.2</v>
       </c>
       <c r="BH14">
         <v>4.3</v>
@@ -5544,34 +5544,34 @@
         <v>4.2</v>
       </c>
       <c r="K15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
         <v>1.28</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
         <v>6</v>
       </c>
       <c r="O15">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P15">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="Q15">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R15">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S15">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T15">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="U15">
         <v>2.46</v>
@@ -5610,10 +5610,10 @@
         <v>17.5</v>
       </c>
       <c r="AG15">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI15">
         <v>55</v>
@@ -5631,46 +5631,46 @@
         <v>85</v>
       </c>
       <c r="AN15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AO15">
         <v>44</v>
       </c>
       <c r="AP15">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="AQ15">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AR15">
-        <v>2.82</v>
+        <v>3.6</v>
       </c>
       <c r="AS15">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="AT15">
-        <v>9.4</v>
+        <v>3.15</v>
       </c>
       <c r="AU15">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AV15">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="AW15">
-        <v>2.84</v>
+        <v>3.65</v>
       </c>
       <c r="AX15">
-        <v>9.4</v>
+        <v>3.15</v>
       </c>
       <c r="AY15">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
         <v>10</v>
       </c>
       <c r="BA15">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="BB15">
         <v>16.5</v>
@@ -5682,10 +5682,10 @@
         <v>18</v>
       </c>
       <c r="BE15">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="BF15">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG15">
         <v>19</v>
@@ -5774,16 +5774,16 @@
         <v>3.75</v>
       </c>
       <c r="G16">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H16">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="I16">
         <v>2</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K16">
         <v>4.4</v>
@@ -5792,19 +5792,19 @@
         <v>1.28</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
         <v>6</v>
       </c>
       <c r="O16">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P16">
         <v>2.66</v>
       </c>
       <c r="Q16">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R16">
         <v>1.67</v>
@@ -5822,7 +5822,7 @@
         <v>2</v>
       </c>
       <c r="W16">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X16">
         <v>32</v>
@@ -5873,7 +5873,7 @@
         <v>65</v>
       </c>
       <c r="AN16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO16">
         <v>9.800000000000001</v>
@@ -5924,10 +5924,10 @@
         <v>5.9</v>
       </c>
       <c r="BE16">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF16">
-        <v>5.5</v>
+        <v>19</v>
       </c>
       <c r="BG16">
         <v>7.6</v>
@@ -6013,28 +6013,28 @@
         <v>407</v>
       </c>
       <c r="F17">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G17">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="H17">
         <v>4.9</v>
       </c>
       <c r="I17">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J17">
         <v>3.55</v>
       </c>
       <c r="K17">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
         <v>3.15</v>
@@ -6043,28 +6043,28 @@
         <v>1.31</v>
       </c>
       <c r="P17">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q17">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="R17">
         <v>1.3</v>
       </c>
       <c r="S17">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T17">
         <v>1.01</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V17">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W17">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X17">
         <v>18.5</v>
@@ -6115,16 +6115,16 @@
         <v>1000</v>
       </c>
       <c r="AN17">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP17">
         <v>10.5</v>
       </c>
       <c r="AQ17">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AR17">
         <v>24</v>
@@ -6151,7 +6151,7 @@
         <v>7.4</v>
       </c>
       <c r="AZ17">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA17">
         <v>42</v>
@@ -6169,7 +6169,7 @@
         <v>70</v>
       </c>
       <c r="BF17">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG17">
         <v>50</v>
@@ -6261,10 +6261,10 @@
         <v>2.2</v>
       </c>
       <c r="H18">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J18">
         <v>4.2</v>
@@ -6273,37 +6273,37 @@
         <v>4.4</v>
       </c>
       <c r="L18">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M18">
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O18">
         <v>1.17</v>
       </c>
       <c r="P18">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Q18">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R18">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="S18">
         <v>2.32</v>
       </c>
       <c r="T18">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="U18">
         <v>2.74</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W18">
         <v>1.83</v>
@@ -6336,7 +6336,7 @@
         <v>18.5</v>
       </c>
       <c r="AG18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH18">
         <v>15</v>
@@ -6360,10 +6360,10 @@
         <v>10.5</v>
       </c>
       <c r="AO18">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AP18">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ18">
         <v>18</v>
@@ -6378,7 +6378,7 @@
         <v>14.5</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV18">
         <v>13</v>
@@ -6387,7 +6387,7 @@
         <v>25</v>
       </c>
       <c r="AX18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY18">
         <v>10</v>
@@ -6414,7 +6414,7 @@
         <v>9</v>
       </c>
       <c r="BG18">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BH18">
         <v>5.5</v>
@@ -6500,163 +6500,163 @@
         <v>2.64</v>
       </c>
       <c r="G19">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="H19">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I19">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J19">
         <v>3.8</v>
       </c>
       <c r="K19">
+        <v>4.2</v>
+      </c>
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.05</v>
+      </c>
+      <c r="N19">
         <v>4.4</v>
       </c>
-      <c r="L19">
-        <v>1.27</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>4.1</v>
-      </c>
       <c r="O19">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P19">
         <v>2.18</v>
       </c>
       <c r="Q19">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R19">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S19">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="T19">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="U19">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="V19">
         <v>1.6</v>
       </c>
       <c r="W19">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="X19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y19">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z19">
+        <v>19</v>
+      </c>
+      <c r="AA19">
+        <v>38</v>
+      </c>
+      <c r="AB19">
+        <v>13.5</v>
+      </c>
+      <c r="AC19">
+        <v>10.5</v>
+      </c>
+      <c r="AD19">
+        <v>12.5</v>
+      </c>
+      <c r="AE19">
+        <v>26</v>
+      </c>
+      <c r="AF19">
+        <v>19.5</v>
+      </c>
+      <c r="AG19">
+        <v>12.5</v>
+      </c>
+      <c r="AH19">
+        <v>19</v>
+      </c>
+      <c r="AI19">
+        <v>36</v>
+      </c>
+      <c r="AJ19">
+        <v>40</v>
+      </c>
+      <c r="AK19">
+        <v>27</v>
+      </c>
+      <c r="AL19">
+        <v>34</v>
+      </c>
+      <c r="AM19">
+        <v>90</v>
+      </c>
+      <c r="AN19">
         <v>22</v>
       </c>
-      <c r="AA19">
-        <v>48</v>
-      </c>
-      <c r="AB19">
+      <c r="AO19">
+        <v>20</v>
+      </c>
+      <c r="AP19">
+        <v>17</v>
+      </c>
+      <c r="AQ19">
+        <v>5.9</v>
+      </c>
+      <c r="AR19">
+        <v>6.8</v>
+      </c>
+      <c r="AS19">
+        <v>8.4</v>
+      </c>
+      <c r="AT19">
+        <v>11.5</v>
+      </c>
+      <c r="AU19">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV19">
+        <v>10.5</v>
+      </c>
+      <c r="AW19">
+        <v>6.8</v>
+      </c>
+      <c r="AX19">
+        <v>16.5</v>
+      </c>
+      <c r="AY19">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19">
         <v>16</v>
       </c>
-      <c r="AC19">
-        <v>11</v>
-      </c>
-      <c r="AD19">
-        <v>14.5</v>
-      </c>
-      <c r="AE19">
-        <v>32</v>
-      </c>
-      <c r="AF19">
-        <v>23</v>
-      </c>
-      <c r="AG19">
-        <v>15.5</v>
-      </c>
-      <c r="AH19">
-        <v>21</v>
-      </c>
-      <c r="AI19">
-        <v>42</v>
-      </c>
-      <c r="AJ19">
-        <v>50</v>
-      </c>
-      <c r="AK19">
-        <v>34</v>
-      </c>
-      <c r="AL19">
-        <v>44</v>
-      </c>
-      <c r="AM19">
-        <v>95</v>
-      </c>
-      <c r="AN19">
-        <v>25</v>
-      </c>
-      <c r="AO19">
-        <v>23</v>
-      </c>
-      <c r="AP19">
-        <v>13</v>
-      </c>
-      <c r="AQ19">
-        <v>9.6</v>
-      </c>
-      <c r="AR19">
-        <v>12.5</v>
-      </c>
-      <c r="AS19">
-        <v>23</v>
-      </c>
-      <c r="AT19">
-        <v>9.6</v>
-      </c>
-      <c r="AU19">
-        <v>7.4</v>
-      </c>
-      <c r="AV19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW19">
-        <v>19</v>
-      </c>
-      <c r="AX19">
-        <v>13.5</v>
-      </c>
-      <c r="AY19">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ19">
-        <v>12.5</v>
-      </c>
       <c r="BA19">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB19">
-        <v>25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC19">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="BD19">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE19">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="BF19">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BG19">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -6778,7 +6778,7 @@
         <v>1.08</v>
       </c>
       <c r="S20">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T20">
         <v>1.01</v>
@@ -6787,10 +6787,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -6984,7 +6984,7 @@
         <v>3.85</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H21">
         <v>1.96</v>
@@ -6993,22 +6993,22 @@
         <v>2.18</v>
       </c>
       <c r="J21">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K21">
         <v>4.4</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P21">
         <v>1.81</v>
@@ -7017,190 +7017,190 @@
         <v>1.98</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
         <v>591</v>
@@ -7223,226 +7223,226 @@
         <v>412</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P22">
         <v>1.24</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
         <v>591</v>
@@ -7465,226 +7465,226 @@
         <v>413</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P23">
-        <v>1.25</v>
+        <v>2.24</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB23" t="s">
         <v>591</v>
@@ -7707,226 +7707,226 @@
         <v>414</v>
       </c>
       <c r="F24">
-        <v>1.4</v>
+        <v>2.26</v>
       </c>
       <c r="G24">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H24">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="I24">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J24">
         <v>3.35</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>5.2</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P24">
         <v>1.8</v>
       </c>
       <c r="Q24">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB24" t="s">
         <v>591</v>
@@ -7949,22 +7949,22 @@
         <v>415</v>
       </c>
       <c r="F25">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="G25">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H25">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="I25">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J25">
         <v>3.45</v>
       </c>
       <c r="K25">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="Q25">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -8191,7 +8191,7 @@
         <v>416</v>
       </c>
       <c r="F26">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="G26">
         <v>2.94</v>
@@ -8221,7 +8221,7 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q26">
         <v>1.98</v>
@@ -8436,16 +8436,16 @@
         <v>3.3</v>
       </c>
       <c r="G27">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H27">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I27">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K27">
         <v>3.65</v>
@@ -8463,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="Q27">
         <v>1.9</v>
@@ -8675,22 +8675,22 @@
         <v>418</v>
       </c>
       <c r="F28">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="G28">
-        <v>1000</v>
+        <v>1.66</v>
       </c>
       <c r="H28">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="I28">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="J28">
-        <v>1.1</v>
+        <v>3.95</v>
       </c>
       <c r="K28">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="Q28">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -8917,22 +8917,22 @@
         <v>419</v>
       </c>
       <c r="F29">
-        <v>1.1</v>
+        <v>1.84</v>
       </c>
       <c r="G29">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H29">
-        <v>1.1</v>
+        <v>1.94</v>
       </c>
       <c r="I29">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J29">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="K29">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -8947,10 +8947,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="Q29">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -9643,19 +9643,19 @@
         <v>422</v>
       </c>
       <c r="F32">
-        <v>2.72</v>
+        <v>1.36</v>
       </c>
       <c r="G32">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="H32">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="I32">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="J32">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K32">
         <v>3.75</v>
@@ -9673,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="Q32">
         <v>2.04</v>
@@ -10369,7 +10369,7 @@
         <v>425</v>
       </c>
       <c r="F35">
-        <v>1.29</v>
+        <v>2.24</v>
       </c>
       <c r="G35">
         <v>2.82</v>
@@ -10384,7 +10384,7 @@
         <v>3.65</v>
       </c>
       <c r="K35">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -10399,10 +10399,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q35">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -10614,13 +10614,13 @@
         <v>1.29</v>
       </c>
       <c r="G36">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H36">
         <v>10</v>
       </c>
       <c r="I36">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J36">
         <v>6.6</v>
@@ -10877,13 +10877,13 @@
         <v>1.07</v>
       </c>
       <c r="N37">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O37">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P37">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q37">
         <v>1.93</v>
@@ -10898,7 +10898,7 @@
         <v>1.75</v>
       </c>
       <c r="U37">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V37">
         <v>0</v>
@@ -10913,7 +10913,7 @@
         <v>11</v>
       </c>
       <c r="Z37">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AA37">
         <v>30</v>
@@ -10943,7 +10943,7 @@
         <v>36</v>
       </c>
       <c r="AJ37">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="AK37">
         <v>40</v>
@@ -10955,7 +10955,7 @@
         <v>1000</v>
       </c>
       <c r="AN37">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO37">
         <v>17.5</v>
@@ -10985,7 +10985,7 @@
         <v>21</v>
       </c>
       <c r="AX37">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY37">
         <v>13</v>
@@ -11009,7 +11009,7 @@
         <v>36</v>
       </c>
       <c r="BF37">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BG37">
         <v>15</v>
@@ -11098,7 +11098,7 @@
         <v>1.7</v>
       </c>
       <c r="G38">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="H38">
         <v>4.7</v>
@@ -11110,7 +11110,7 @@
         <v>3.45</v>
       </c>
       <c r="K38">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -11125,10 +11125,10 @@
         <v>0</v>
       </c>
       <c r="P38">
+        <v>1.25</v>
+      </c>
+      <c r="Q38">
         <v>1.84</v>
-      </c>
-      <c r="Q38">
-        <v>1.94</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -11337,10 +11337,10 @@
         <v>429</v>
       </c>
       <c r="F39">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G39">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H39">
         <v>4.6</v>
@@ -11361,22 +11361,22 @@
         <v>1.07</v>
       </c>
       <c r="N39">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O39">
         <v>1.31</v>
       </c>
       <c r="P39">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="Q39">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="R39">
         <v>1.37</v>
       </c>
       <c r="S39">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T39">
         <v>1.86</v>
@@ -11412,7 +11412,7 @@
         <v>19</v>
       </c>
       <c r="AE39">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="AF39">
         <v>11.5</v>
@@ -11427,7 +11427,7 @@
         <v>1000</v>
       </c>
       <c r="AJ39">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK39">
         <v>21</v>
@@ -11448,7 +11448,7 @@
         <v>13</v>
       </c>
       <c r="AQ39">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR39">
         <v>21</v>
@@ -11460,7 +11460,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU39">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV39">
         <v>16</v>
@@ -11481,7 +11481,7 @@
         <v>32</v>
       </c>
       <c r="BB39">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC39">
         <v>17</v>
@@ -11493,7 +11493,7 @@
         <v>40</v>
       </c>
       <c r="BF39">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG39">
         <v>32</v>
@@ -11579,7 +11579,7 @@
         <v>430</v>
       </c>
       <c r="F40">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="G40">
         <v>4.1</v>
@@ -11612,7 +11612,7 @@
         <v>1.92</v>
       </c>
       <c r="Q40">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -11824,19 +11824,19 @@
         <v>2.32</v>
       </c>
       <c r="G41">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H41">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I41">
         <v>3.25</v>
       </c>
       <c r="J41">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K41">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -11845,28 +11845,28 @@
         <v>1.04</v>
       </c>
       <c r="N41">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O41">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P41">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q41">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="R41">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S41">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="T41">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U41">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -11875,7 +11875,7 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y41">
         <v>19.5</v>
@@ -11893,13 +11893,13 @@
         <v>9.6</v>
       </c>
       <c r="AD41">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE41">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AF41">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AG41">
         <v>12.5</v>
@@ -11929,52 +11929,52 @@
         <v>19.5</v>
       </c>
       <c r="AP41">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ41">
+        <v>16.5</v>
+      </c>
+      <c r="AR41">
+        <v>21</v>
+      </c>
+      <c r="AS41">
+        <v>9.6</v>
+      </c>
+      <c r="AT41">
+        <v>14</v>
+      </c>
+      <c r="AU41">
         <v>8</v>
-      </c>
-      <c r="AR41">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS41">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT41">
-        <v>13.5</v>
-      </c>
-      <c r="AU41">
-        <v>8.4</v>
       </c>
       <c r="AV41">
         <v>12.5</v>
       </c>
       <c r="AW41">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX41">
         <v>16</v>
       </c>
       <c r="AY41">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ41">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA41">
+        <v>7.8</v>
+      </c>
+      <c r="BB41">
         <v>9.4</v>
       </c>
-      <c r="BB41">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BC41">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD41">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BE41">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF41">
         <v>10</v>
@@ -11986,7 +11986,7 @@
         <v>1000</v>
       </c>
       <c r="BI41">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ41">
         <v>1000</v>
@@ -12096,7 +12096,7 @@
         <v>2.16</v>
       </c>
       <c r="Q42">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -13031,22 +13031,22 @@
         <v>436</v>
       </c>
       <c r="F46">
+        <v>3.25</v>
+      </c>
+      <c r="G46">
         <v>3.3</v>
       </c>
-      <c r="G46">
-        <v>3.35</v>
-      </c>
       <c r="H46">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I46">
         <v>2.2</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K46">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -13518,10 +13518,10 @@
         <v>2.12</v>
       </c>
       <c r="G48">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H48">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I48">
         <v>3.55</v>
@@ -13760,19 +13760,19 @@
         <v>1.83</v>
       </c>
       <c r="G49">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H49">
+        <v>4.1</v>
+      </c>
+      <c r="I49">
+        <v>5</v>
+      </c>
+      <c r="J49">
         <v>4</v>
       </c>
-      <c r="I49">
-        <v>5.6</v>
-      </c>
-      <c r="J49">
-        <v>3.8</v>
-      </c>
       <c r="K49">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -13790,7 +13790,7 @@
         <v>1.25</v>
       </c>
       <c r="Q49">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -13999,22 +13999,22 @@
         <v>440</v>
       </c>
       <c r="F50">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="G50">
+        <v>2.6</v>
+      </c>
+      <c r="H50">
         <v>2.52</v>
       </c>
-      <c r="H50">
-        <v>2.98</v>
-      </c>
       <c r="I50">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="J50">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K50">
-        <v>6.4</v>
+        <v>5</v>
       </c>
       <c r="L50">
         <v>0</v>
@@ -14029,10 +14029,10 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q50">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="R50">
         <v>0</v>
@@ -14486,19 +14486,19 @@
         <v>4.9</v>
       </c>
       <c r="G52">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="H52">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="I52">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="J52">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K52">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="L52">
         <v>0</v>
@@ -14513,10 +14513,10 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q52">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -14970,7 +14970,7 @@
         <v>2.4</v>
       </c>
       <c r="G54">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H54">
         <v>2.56</v>
@@ -14997,10 +14997,10 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q54">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -15209,13 +15209,13 @@
         <v>445</v>
       </c>
       <c r="F55">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G55">
         <v>2.4</v>
       </c>
       <c r="H55">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I55">
         <v>3.35</v>
@@ -15224,7 +15224,7 @@
         <v>3.5</v>
       </c>
       <c r="K55">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -15239,7 +15239,7 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q55">
         <v>1.46</v>
@@ -15451,16 +15451,16 @@
         <v>446</v>
       </c>
       <c r="F56">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="G56">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H56">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I56">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J56">
         <v>3.65</v>
@@ -15484,7 +15484,7 @@
         <v>2.1</v>
       </c>
       <c r="Q56">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -15699,7 +15699,7 @@
         <v>1.72</v>
       </c>
       <c r="H57">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I57">
         <v>1000</v>
@@ -15726,7 +15726,7 @@
         <v>2.38</v>
       </c>
       <c r="Q57">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -15935,22 +15935,22 @@
         <v>448</v>
       </c>
       <c r="F58">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G58">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H58">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="I58">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="J58">
         <v>3.75</v>
       </c>
       <c r="K58">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="L58">
         <v>0</v>
@@ -15965,10 +15965,10 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q58">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R58">
         <v>0</v>
@@ -16210,7 +16210,7 @@
         <v>1.5</v>
       </c>
       <c r="Q59">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="R59">
         <v>0</v>
@@ -16419,19 +16419,19 @@
         <v>450</v>
       </c>
       <c r="F60">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G60">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H60">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I60">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J60">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K60">
         <v>3.2</v>
@@ -16446,7 +16446,7 @@
         <v>2.52</v>
       </c>
       <c r="O60">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P60">
         <v>1.51</v>
@@ -16491,13 +16491,13 @@
         <v>7.4</v>
       </c>
       <c r="AD60">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE60">
         <v>95</v>
       </c>
       <c r="AF60">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG60">
         <v>12</v>
@@ -16533,7 +16533,7 @@
         <v>10</v>
       </c>
       <c r="AR60">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS60">
         <v>38</v>
@@ -16548,7 +16548,7 @@
         <v>18</v>
       </c>
       <c r="AW60">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX60">
         <v>10</v>
@@ -16661,23 +16661,23 @@
         <v>451</v>
       </c>
       <c r="F61">
+        <v>6.6</v>
+      </c>
+      <c r="G61">
+        <v>16.5</v>
+      </c>
+      <c r="H61">
+        <v>1.46</v>
+      </c>
+      <c r="I61">
+        <v>1.68</v>
+      </c>
+      <c r="J61">
+        <v>3.95</v>
+      </c>
+      <c r="K61">
         <v>6.2</v>
       </c>
-      <c r="G61">
-        <v>36</v>
-      </c>
-      <c r="H61">
-        <v>1.44</v>
-      </c>
-      <c r="I61">
-        <v>1.73</v>
-      </c>
-      <c r="J61">
-        <v>3.6</v>
-      </c>
-      <c r="K61">
-        <v>6.8</v>
-      </c>
       <c r="L61">
         <v>0</v>
       </c>
@@ -16691,10 +16691,10 @@
         <v>0</v>
       </c>
       <c r="P61">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q61">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -16903,16 +16903,16 @@
         <v>452</v>
       </c>
       <c r="F62">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="G62">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="H62">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="I62">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J62">
         <v>3.85</v>
@@ -17145,19 +17145,19 @@
         <v>453</v>
       </c>
       <c r="F63">
-        <v>2.9</v>
+        <v>2.46</v>
       </c>
       <c r="G63">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="H63">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I63">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="J63">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K63">
         <v>4.7</v>
@@ -17175,10 +17175,10 @@
         <v>0</v>
       </c>
       <c r="P63">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q63">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -17396,13 +17396,13 @@
         <v>3.6</v>
       </c>
       <c r="I64">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J64">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K64">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L64">
         <v>0</v>
@@ -17644,7 +17644,7 @@
         <v>1.1</v>
       </c>
       <c r="K65">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L65">
         <v>1.01</v>
@@ -17871,19 +17871,19 @@
         <v>456</v>
       </c>
       <c r="F66">
-        <v>2.66</v>
+        <v>2.32</v>
       </c>
       <c r="G66">
         <v>3.15</v>
       </c>
       <c r="H66">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="I66">
         <v>3</v>
       </c>
       <c r="J66">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K66">
         <v>4.2</v>
@@ -18355,7 +18355,7 @@
         <v>458</v>
       </c>
       <c r="F68">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G68">
         <v>2.08</v>
@@ -18364,7 +18364,7 @@
         <v>3.6</v>
       </c>
       <c r="I68">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J68">
         <v>4.1</v>
@@ -18385,7 +18385,7 @@
         <v>0</v>
       </c>
       <c r="P68">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q68">
         <v>1.53</v>
@@ -18603,7 +18603,7 @@
         <v>1.59</v>
       </c>
       <c r="H69">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I69">
         <v>6.4</v>
@@ -18618,7 +18618,7 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N69">
         <v>0</v>
@@ -18627,7 +18627,7 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q69">
         <v>1.56</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="T69">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U69">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V69">
         <v>0</v>
@@ -18657,7 +18657,7 @@
         <v>29</v>
       </c>
       <c r="Z69">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="AA69">
         <v>1000</v>
@@ -18705,25 +18705,25 @@
         <v>1000</v>
       </c>
       <c r="AP69">
+        <v>18</v>
+      </c>
+      <c r="AQ69">
         <v>18.5</v>
       </c>
-      <c r="AQ69">
-        <v>18</v>
-      </c>
       <c r="AR69">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS69">
         <v>44</v>
       </c>
       <c r="AT69">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU69">
         <v>10</v>
       </c>
       <c r="AV69">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AW69">
         <v>32</v>
@@ -18732,16 +18732,16 @@
         <v>10</v>
       </c>
       <c r="AY69">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ69">
         <v>16.5</v>
       </c>
       <c r="BA69">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB69">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC69">
         <v>13</v>
@@ -18756,7 +18756,7 @@
         <v>5.7</v>
       </c>
       <c r="BG69">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH69">
         <v>0</v>
@@ -19081,22 +19081,22 @@
         <v>461</v>
       </c>
       <c r="F71">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G71">
         <v>3.15</v>
       </c>
       <c r="H71">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I71">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="J71">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K71">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -19111,7 +19111,7 @@
         <v>0</v>
       </c>
       <c r="P71">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="Q71">
         <v>1.25</v>
@@ -19323,19 +19323,19 @@
         <v>462</v>
       </c>
       <c r="F72">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="G72">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H72">
         <v>3.8</v>
       </c>
       <c r="I72">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J72">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K72">
         <v>4.4</v>
@@ -19356,7 +19356,7 @@
         <v>2</v>
       </c>
       <c r="Q72">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -19598,7 +19598,7 @@
         <v>2.72</v>
       </c>
       <c r="Q73">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R73">
         <v>0</v>
@@ -19807,19 +19807,19 @@
         <v>464</v>
       </c>
       <c r="F74">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G74">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="H74">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I74">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J74">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="K74">
         <v>7.8</v>
@@ -20049,22 +20049,22 @@
         <v>465</v>
       </c>
       <c r="F75">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G75">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H75">
         <v>2.72</v>
       </c>
       <c r="I75">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J75">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K75">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -20079,7 +20079,7 @@
         <v>0</v>
       </c>
       <c r="P75">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q75">
         <v>1.33</v>
@@ -20291,22 +20291,22 @@
         <v>466</v>
       </c>
       <c r="F76">
-        <v>1.1</v>
+        <v>2.44</v>
       </c>
       <c r="G76">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="H76">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="I76">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J76">
         <v>3.15</v>
       </c>
       <c r="K76">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -20324,7 +20324,7 @@
         <v>1.25</v>
       </c>
       <c r="Q76">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R76">
         <v>0</v>
@@ -20775,22 +20775,22 @@
         <v>468</v>
       </c>
       <c r="F78">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G78">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H78">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I78">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J78">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K78">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -20805,10 +20805,10 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q78">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -21274,7 +21274,7 @@
         <v>1.1</v>
       </c>
       <c r="K80">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L80">
         <v>0</v>
@@ -21755,7 +21755,7 @@
         <v>4.3</v>
       </c>
       <c r="J82">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K82">
         <v>3.35</v>
@@ -21773,7 +21773,7 @@
         <v>0</v>
       </c>
       <c r="P82">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q82">
         <v>2.38</v>
@@ -22227,7 +22227,7 @@
         <v>474</v>
       </c>
       <c r="F84">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G84">
         <v>3.35</v>
@@ -22236,7 +22236,7 @@
         <v>2.64</v>
       </c>
       <c r="I84">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J84">
         <v>3.1</v>
@@ -22257,7 +22257,7 @@
         <v>1.52</v>
       </c>
       <c r="P84">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q84">
         <v>2.58</v>
@@ -22478,10 +22478,10 @@
         <v>1.56</v>
       </c>
       <c r="I85">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J85">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K85">
         <v>4.9</v>
@@ -22493,13 +22493,13 @@
         <v>1.03</v>
       </c>
       <c r="N85">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O85">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P85">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q85">
         <v>1.49</v>
@@ -22511,10 +22511,10 @@
         <v>2.2</v>
       </c>
       <c r="T85">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U85">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V85">
         <v>0</v>
@@ -22529,10 +22529,10 @@
         <v>14</v>
       </c>
       <c r="Z85">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA85">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AB85">
         <v>34</v>
@@ -22550,7 +22550,7 @@
         <v>65</v>
       </c>
       <c r="AG85">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH85">
         <v>17</v>
@@ -22559,19 +22559,19 @@
         <v>24</v>
       </c>
       <c r="AJ85">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK85">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL85">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM85">
         <v>65</v>
       </c>
       <c r="AN85">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO85">
         <v>5.4</v>
@@ -22580,25 +22580,25 @@
         <v>19</v>
       </c>
       <c r="AQ85">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR85">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS85">
         <v>15</v>
       </c>
       <c r="AT85">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AU85">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV85">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW85">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AX85">
         <v>30</v>
@@ -22613,19 +22613,19 @@
         <v>21</v>
       </c>
       <c r="BB85">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC85">
         <v>32</v>
       </c>
       <c r="BD85">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE85">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BF85">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BG85">
         <v>5.1</v>
@@ -22711,16 +22711,16 @@
         <v>476</v>
       </c>
       <c r="F86">
+        <v>1.81</v>
+      </c>
+      <c r="G86">
         <v>1.82</v>
       </c>
-      <c r="G86">
-        <v>1.84</v>
-      </c>
       <c r="H86">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I86">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J86">
         <v>3.95</v>
@@ -22813,7 +22813,7 @@
         <v>85</v>
       </c>
       <c r="AN86">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO86">
         <v>55</v>
@@ -22822,7 +22822,7 @@
         <v>16</v>
       </c>
       <c r="AQ86">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR86">
         <v>34</v>
@@ -22834,7 +22834,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU86">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV86">
         <v>17</v>
@@ -22846,7 +22846,7 @@
         <v>11</v>
       </c>
       <c r="AY86">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ86">
         <v>15.5</v>
@@ -22885,7 +22885,7 @@
         <v>8.6</v>
       </c>
       <c r="BL86">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="BM86">
         <v>12.5</v>
@@ -23010,13 +23010,13 @@
         <v>25</v>
       </c>
       <c r="Y87">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z87">
         <v>1000</v>
       </c>
       <c r="AA87">
-        <v>500</v>
+        <v>510</v>
       </c>
       <c r="AB87">
         <v>9.4</v>
@@ -23025,7 +23025,7 @@
         <v>13.5</v>
       </c>
       <c r="AD87">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AE87">
         <v>1000</v>
@@ -23037,7 +23037,7 @@
         <v>10.5</v>
       </c>
       <c r="AH87">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI87">
         <v>1000</v>
@@ -23052,10 +23052,10 @@
         <v>38</v>
       </c>
       <c r="AM87">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN87">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AO87">
         <v>1000</v>
@@ -23106,7 +23106,7 @@
         <v>23</v>
       </c>
       <c r="BE87">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF87">
         <v>4.7</v>
@@ -23118,7 +23118,7 @@
         <v>820</v>
       </c>
       <c r="BI87">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ87">
         <v>1000</v>
@@ -23207,7 +23207,7 @@
         <v>2.26</v>
       </c>
       <c r="J88">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K88">
         <v>4.1</v>
@@ -23273,7 +23273,7 @@
         <v>19.5</v>
       </c>
       <c r="AF88">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG88">
         <v>14.5</v>
@@ -23303,7 +23303,7 @@
         <v>10</v>
       </c>
       <c r="AP88">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ88">
         <v>15</v>
@@ -23318,7 +23318,7 @@
         <v>19</v>
       </c>
       <c r="AU88">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV88">
         <v>10.5</v>
@@ -23330,7 +23330,7 @@
         <v>26</v>
       </c>
       <c r="AY88">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ88">
         <v>12</v>
@@ -23348,13 +23348,13 @@
         <v>28</v>
       </c>
       <c r="BE88">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF88">
         <v>16</v>
       </c>
       <c r="BG88">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH88">
         <v>970</v>
@@ -23682,16 +23682,16 @@
         <v>1.43</v>
       </c>
       <c r="G90">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="H90">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="I90">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J90">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K90">
         <v>5.2</v>
@@ -23709,7 +23709,7 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="Q90">
         <v>1.74</v>
@@ -23924,19 +23924,19 @@
         <v>3.05</v>
       </c>
       <c r="G91">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H91">
         <v>2.26</v>
       </c>
       <c r="I91">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J91">
         <v>3.7</v>
       </c>
       <c r="K91">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L91">
         <v>0</v>
@@ -23951,10 +23951,10 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q91">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -24163,22 +24163,22 @@
         <v>482</v>
       </c>
       <c r="F92">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G92">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H92">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I92">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J92">
+        <v>3.65</v>
+      </c>
+      <c r="K92">
         <v>3.75</v>
-      </c>
-      <c r="K92">
-        <v>3.85</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -24193,13 +24193,13 @@
         <v>1.28</v>
       </c>
       <c r="P92">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q92">
         <v>1.8</v>
       </c>
       <c r="R92">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S92">
         <v>3.05</v>
@@ -24223,7 +24223,7 @@
         <v>12.5</v>
       </c>
       <c r="Z92">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA92">
         <v>34</v>
@@ -24232,7 +24232,7 @@
         <v>14</v>
       </c>
       <c r="AC92">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD92">
         <v>12</v>
@@ -24262,13 +24262,13 @@
         <v>40</v>
       </c>
       <c r="AM92">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN92">
         <v>27</v>
       </c>
       <c r="AO92">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AP92">
         <v>15.5</v>
@@ -24286,7 +24286,7 @@
         <v>12</v>
       </c>
       <c r="AU92">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV92">
         <v>10.5</v>
@@ -24301,28 +24301,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ92">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA92">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB92">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC92">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD92">
         <v>8.4</v>
       </c>
-      <c r="BB92">
-        <v>9</v>
-      </c>
-      <c r="BC92">
-        <v>9.4</v>
-      </c>
-      <c r="BD92">
-        <v>8.6</v>
-      </c>
       <c r="BE92">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF92">
         <v>21</v>
       </c>
       <c r="BG92">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH92">
         <v>970</v>
@@ -24408,19 +24408,19 @@
         <v>2.04</v>
       </c>
       <c r="G93">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H93">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I93">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J93">
         <v>4.3</v>
       </c>
       <c r="K93">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -24438,13 +24438,13 @@
         <v>3.4</v>
       </c>
       <c r="Q93">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R93">
         <v>1.99</v>
       </c>
       <c r="S93">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="T93">
         <v>1.4</v>
@@ -24477,10 +24477,10 @@
         <v>11.5</v>
       </c>
       <c r="AD93">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE93">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF93">
         <v>21</v>
@@ -24507,10 +24507,10 @@
         <v>40</v>
       </c>
       <c r="AN93">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AO93">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP93">
         <v>32</v>
@@ -24555,7 +24555,7 @@
         <v>16</v>
       </c>
       <c r="BD93">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE93">
         <v>30</v>
@@ -24656,13 +24656,13 @@
         <v>1.37</v>
       </c>
       <c r="I94">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="J94">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="K94">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -24889,7 +24889,7 @@
         <v>485</v>
       </c>
       <c r="F95">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="G95">
         <v>3.05</v>
@@ -25134,16 +25134,16 @@
         <v>1.08</v>
       </c>
       <c r="G96">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="H96">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="I96">
         <v>1000</v>
       </c>
       <c r="J96">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="K96">
         <v>1000</v>
@@ -25164,7 +25164,7 @@
         <v>1.25</v>
       </c>
       <c r="Q96">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -25388,7 +25388,7 @@
         <v>5.3</v>
       </c>
       <c r="K97">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -26102,7 +26102,7 @@
         <v>4.3</v>
       </c>
       <c r="G100">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H100">
         <v>1.89</v>
@@ -26111,7 +26111,7 @@
         <v>1.91</v>
       </c>
       <c r="J100">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K100">
         <v>3.9</v>
@@ -26129,7 +26129,7 @@
         <v>0</v>
       </c>
       <c r="P100">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q100">
         <v>1.94</v>
@@ -26347,7 +26347,7 @@
         <v>4.5</v>
       </c>
       <c r="H101">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I101">
         <v>2.04</v>
@@ -26583,16 +26583,16 @@
         <v>492</v>
       </c>
       <c r="F102">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G102">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H102">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I102">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="J102">
         <v>4.4</v>
@@ -26613,10 +26613,10 @@
         <v>0</v>
       </c>
       <c r="P102">
-        <v>2.78</v>
+        <v>1.25</v>
       </c>
       <c r="Q102">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -26825,7 +26825,7 @@
         <v>493</v>
       </c>
       <c r="F103">
-        <v>1.12</v>
+        <v>3.25</v>
       </c>
       <c r="G103">
         <v>150</v>
@@ -26840,7 +26840,7 @@
         <v>4.7</v>
       </c>
       <c r="K103">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L103">
         <v>1.01</v>
@@ -26864,7 +26864,7 @@
         <v>1.35</v>
       </c>
       <c r="S103">
-        <v>2.52</v>
+        <v>2.14</v>
       </c>
       <c r="T103">
         <v>1.01</v>
@@ -27079,10 +27079,10 @@
         <v>2.02</v>
       </c>
       <c r="J104">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K104">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -27097,13 +27097,13 @@
         <v>1.16</v>
       </c>
       <c r="P104">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="Q104">
         <v>1.5</v>
       </c>
       <c r="R104">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="S104">
         <v>2.2</v>
@@ -27124,7 +27124,7 @@
         <v>32</v>
       </c>
       <c r="Y104">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z104">
         <v>17</v>
@@ -27160,7 +27160,7 @@
         <v>75</v>
       </c>
       <c r="AK104">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL104">
         <v>36</v>
@@ -27169,7 +27169,7 @@
         <v>50</v>
       </c>
       <c r="AN104">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO104">
         <v>8</v>
@@ -27181,7 +27181,7 @@
         <v>14.5</v>
       </c>
       <c r="AR104">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS104">
         <v>23</v>
@@ -27223,16 +27223,16 @@
         <v>34</v>
       </c>
       <c r="BF104">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG104">
         <v>7.4</v>
       </c>
       <c r="BH104">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BI104">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ104">
         <v>11.5</v>
@@ -27315,13 +27315,13 @@
         <v>2.84</v>
       </c>
       <c r="H105">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I105">
         <v>2.78</v>
       </c>
       <c r="J105">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K105">
         <v>3.6</v>
@@ -27342,7 +27342,7 @@
         <v>1.25</v>
       </c>
       <c r="Q105">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -27566,7 +27566,7 @@
         <v>4</v>
       </c>
       <c r="K106">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L106">
         <v>0</v>
@@ -27584,7 +27584,7 @@
         <v>2.92</v>
       </c>
       <c r="Q106">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="R106">
         <v>0</v>
@@ -27793,22 +27793,22 @@
         <v>497</v>
       </c>
       <c r="F107">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="G107">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="H107">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="I107">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="J107">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="K107">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="L107">
         <v>0</v>
@@ -27823,10 +27823,10 @@
         <v>0</v>
       </c>
       <c r="P107">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="Q107">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="R107">
         <v>0</v>
@@ -28035,10 +28035,10 @@
         <v>498</v>
       </c>
       <c r="F108">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G108">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H108">
         <v>2.44</v>
@@ -28283,16 +28283,16 @@
         <v>4.5</v>
       </c>
       <c r="H109">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I109">
         <v>2.04</v>
       </c>
       <c r="J109">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K109">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L109">
         <v>0</v>
@@ -28307,10 +28307,10 @@
         <v>0</v>
       </c>
       <c r="P109">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="Q109">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R109">
         <v>0</v>
@@ -28519,22 +28519,22 @@
         <v>500</v>
       </c>
       <c r="F110">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G110">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H110">
         <v>7</v>
       </c>
       <c r="I110">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="J110">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K110">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -28549,7 +28549,7 @@
         <v>0</v>
       </c>
       <c r="P110">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="Q110">
         <v>1.88</v>
@@ -28561,10 +28561,10 @@
         <v>0</v>
       </c>
       <c r="T110">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="U110">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="V110">
         <v>0</v>
@@ -28633,13 +28633,13 @@
         <v>19</v>
       </c>
       <c r="AR110">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AS110">
         <v>10.5</v>
       </c>
       <c r="AT110">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU110">
         <v>8.800000000000001</v>
@@ -28648,7 +28648,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AW110">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX110">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>9</v>
       </c>
       <c r="AZ110">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA110">
         <v>10</v>
@@ -28669,13 +28669,13 @@
         <v>15.5</v>
       </c>
       <c r="BD110">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BE110">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF110">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG110">
         <v>10.5</v>
@@ -29006,13 +29006,13 @@
         <v>2.24</v>
       </c>
       <c r="G112">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H112">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I112">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J112">
         <v>3.3</v>
@@ -29069,7 +29069,7 @@
         <v>85</v>
       </c>
       <c r="AB112">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC112">
         <v>7.6</v>
@@ -29111,7 +29111,7 @@
         <v>60</v>
       </c>
       <c r="AP112">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AQ112">
         <v>11</v>
@@ -29120,7 +29120,7 @@
         <v>18</v>
       </c>
       <c r="AS112">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT112">
         <v>8.199999999999999</v>
@@ -29132,7 +29132,7 @@
         <v>13.5</v>
       </c>
       <c r="AW112">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX112">
         <v>12.5</v>
@@ -29144,7 +29144,7 @@
         <v>16.5</v>
       </c>
       <c r="BA112">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB112">
         <v>7.4</v>
@@ -29153,16 +29153,16 @@
         <v>18.5</v>
       </c>
       <c r="BD112">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE112">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF112">
         <v>19</v>
       </c>
       <c r="BG112">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH112">
         <v>0</v>
@@ -29245,22 +29245,22 @@
         <v>503</v>
       </c>
       <c r="F113">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="G113">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="H113">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="I113">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="J113">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="K113">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L113">
         <v>0</v>
@@ -29275,10 +29275,10 @@
         <v>0</v>
       </c>
       <c r="P113">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="Q113">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -29490,13 +29490,13 @@
         <v>3.3</v>
       </c>
       <c r="G114">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H114">
         <v>1.74</v>
       </c>
       <c r="I114">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="J114">
         <v>3.95</v>
@@ -29732,10 +29732,10 @@
         <v>1.99</v>
       </c>
       <c r="G115">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H115">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I115">
         <v>3.75</v>
@@ -29762,7 +29762,7 @@
         <v>1.25</v>
       </c>
       <c r="Q115">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="R115">
         <v>0</v>
@@ -29971,22 +29971,22 @@
         <v>506</v>
       </c>
       <c r="F116">
-        <v>2.14</v>
+        <v>1.13</v>
       </c>
       <c r="G116">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H116">
-        <v>2.9</v>
+        <v>1.61</v>
       </c>
       <c r="I116">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J116">
-        <v>3.4</v>
+        <v>1.76</v>
       </c>
       <c r="K116">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="L116">
         <v>0</v>
@@ -30001,10 +30001,10 @@
         <v>0</v>
       </c>
       <c r="P116">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q116">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="R116">
         <v>0</v>
@@ -30455,22 +30455,22 @@
         <v>508</v>
       </c>
       <c r="F118">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G118">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H118">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I118">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J118">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K118">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L118">
         <v>0</v>
@@ -30485,7 +30485,7 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q118">
         <v>1.71</v>
@@ -30712,7 +30712,7 @@
         <v>2.98</v>
       </c>
       <c r="K119">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -30939,19 +30939,19 @@
         <v>510</v>
       </c>
       <c r="F120">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G120">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H120">
         <v>3.2</v>
       </c>
       <c r="I120">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J120">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K120">
         <v>4</v>
@@ -31181,22 +31181,22 @@
         <v>511</v>
       </c>
       <c r="F121">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G121">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H121">
         <v>5.9</v>
       </c>
       <c r="I121">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="J121">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K121">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="L121">
         <v>0</v>
@@ -31214,7 +31214,7 @@
         <v>2.28</v>
       </c>
       <c r="Q121">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R121">
         <v>0</v>
@@ -31426,19 +31426,19 @@
         <v>1.44</v>
       </c>
       <c r="G122">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="H122">
         <v>5.3</v>
       </c>
       <c r="I122">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J122">
         <v>4.7</v>
       </c>
       <c r="K122">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L122">
         <v>0</v>
@@ -31665,7 +31665,7 @@
         <v>513</v>
       </c>
       <c r="F123">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="G123">
         <v>1.41</v>
@@ -31674,13 +31674,13 @@
         <v>9</v>
       </c>
       <c r="I123">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="J123">
         <v>5.6</v>
       </c>
       <c r="K123">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L123">
         <v>0</v>
@@ -31695,7 +31695,7 @@
         <v>0</v>
       </c>
       <c r="P123">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="Q123">
         <v>1.23</v>
@@ -31907,22 +31907,22 @@
         <v>514</v>
       </c>
       <c r="F124">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="G124">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H124">
-        <v>3.45</v>
+        <v>2.74</v>
       </c>
       <c r="I124">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="J124">
-        <v>4.4</v>
+        <v>1.96</v>
       </c>
       <c r="K124">
-        <v>7.2</v>
+        <v>110</v>
       </c>
       <c r="L124">
         <v>0</v>
@@ -31937,7 +31937,7 @@
         <v>0</v>
       </c>
       <c r="P124">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="Q124">
         <v>1.18</v>
@@ -32179,10 +32179,10 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="Q125">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -32391,7 +32391,7 @@
         <v>516</v>
       </c>
       <c r="F126">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="G126">
         <v>1.52</v>
@@ -32400,13 +32400,13 @@
         <v>5.8</v>
       </c>
       <c r="I126">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J126">
         <v>4.2</v>
       </c>
       <c r="K126">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="L126">
         <v>0</v>
@@ -32421,10 +32421,10 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q126">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -32639,16 +32639,16 @@
         <v>1.91</v>
       </c>
       <c r="H127">
-        <v>3.9</v>
+        <v>2.08</v>
       </c>
       <c r="I127">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="J127">
         <v>2.08</v>
       </c>
       <c r="K127">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L127">
         <v>0</v>
@@ -32666,7 +32666,7 @@
         <v>3</v>
       </c>
       <c r="Q127">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -32875,10 +32875,10 @@
         <v>518</v>
       </c>
       <c r="F128">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="G128">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H128">
         <v>1.3</v>
@@ -32887,10 +32887,10 @@
         <v>1.39</v>
       </c>
       <c r="J128">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="K128">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="L128">
         <v>0</v>
@@ -32905,10 +32905,10 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>3.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q128">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -33132,7 +33132,7 @@
         <v>1.1</v>
       </c>
       <c r="K129">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L129">
         <v>0</v>
@@ -33359,22 +33359,22 @@
         <v>520</v>
       </c>
       <c r="F130">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="G130">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="H130">
         <v>3.7</v>
       </c>
       <c r="I130">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J130">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K130">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L130">
         <v>0</v>
@@ -33389,10 +33389,10 @@
         <v>0</v>
       </c>
       <c r="P130">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q130">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="R130">
         <v>0</v>
@@ -33846,16 +33846,16 @@
         <v>1.77</v>
       </c>
       <c r="G132">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="H132">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I132">
         <v>5</v>
       </c>
       <c r="J132">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K132">
         <v>4.2</v>
@@ -33873,10 +33873,10 @@
         <v>0</v>
       </c>
       <c r="P132">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q132">
-        <v>1.92</v>
+        <v>1.02</v>
       </c>
       <c r="R132">
         <v>0</v>
@@ -34327,22 +34327,22 @@
         <v>524</v>
       </c>
       <c r="F134">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="G134">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H134">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I134">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J134">
         <v>4.4</v>
       </c>
       <c r="K134">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L134">
         <v>0</v>
@@ -34357,10 +34357,10 @@
         <v>0</v>
       </c>
       <c r="P134">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q134">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R134">
         <v>0</v>
@@ -34569,16 +34569,16 @@
         <v>525</v>
       </c>
       <c r="F135">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G135">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H135">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I135">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J135">
         <v>3.2</v>
@@ -34823,7 +34823,7 @@
         <v>2.2</v>
       </c>
       <c r="J136">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K136">
         <v>3.75</v>
@@ -34835,7 +34835,7 @@
         <v>1.07</v>
       </c>
       <c r="N136">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O136">
         <v>1.32</v>
@@ -34889,7 +34889,7 @@
         <v>24</v>
       </c>
       <c r="AF136">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG136">
         <v>16.5</v>
@@ -34901,7 +34901,7 @@
         <v>42</v>
       </c>
       <c r="AJ136">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK136">
         <v>60</v>
@@ -34943,7 +34943,7 @@
         <v>20</v>
       </c>
       <c r="AX136">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="AY136">
         <v>14</v>
@@ -34952,22 +34952,22 @@
         <v>15.5</v>
       </c>
       <c r="BA136">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB136">
         <v>9.800000000000001</v>
       </c>
       <c r="BC136">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD136">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE136">
         <v>10</v>
       </c>
       <c r="BF136">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BG136">
         <v>14</v>
@@ -35092,7 +35092,7 @@
         <v>1.63</v>
       </c>
       <c r="S137">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="T137">
         <v>1.56</v>
@@ -35170,7 +35170,7 @@
         <v>14.5</v>
       </c>
       <c r="AS137">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT137">
         <v>18</v>
@@ -35185,7 +35185,7 @@
         <v>17</v>
       </c>
       <c r="AX137">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY137">
         <v>13.5</v>
@@ -35212,7 +35212,7 @@
         <v>22</v>
       </c>
       <c r="BG137">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH137">
         <v>4.9</v>
@@ -35298,13 +35298,13 @@
         <v>2.1</v>
       </c>
       <c r="G138">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H138">
         <v>3.7</v>
       </c>
       <c r="I138">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J138">
         <v>3.85</v>
@@ -35337,7 +35337,7 @@
         <v>2.26</v>
       </c>
       <c r="T138">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="U138">
         <v>2.86</v>
@@ -35364,13 +35364,13 @@
         <v>16.5</v>
       </c>
       <c r="AC138">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD138">
         <v>16.5</v>
       </c>
       <c r="AE138">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AF138">
         <v>18.5</v>
@@ -35385,7 +35385,7 @@
         <v>36</v>
       </c>
       <c r="AJ138">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK138">
         <v>19.5</v>
@@ -35406,7 +35406,7 @@
         <v>21</v>
       </c>
       <c r="AQ138">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AR138">
         <v>21</v>
@@ -35418,7 +35418,7 @@
         <v>13.5</v>
       </c>
       <c r="AU138">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV138">
         <v>14.5</v>
@@ -35537,13 +35537,13 @@
         <v>529</v>
       </c>
       <c r="F139">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G139">
         <v>3.3</v>
       </c>
       <c r="H139">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I139">
         <v>2.6</v>
@@ -36989,22 +36989,22 @@
         <v>535</v>
       </c>
       <c r="F145">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G145">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H145">
         <v>3.1</v>
       </c>
       <c r="I145">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J145">
-        <v>3.1</v>
+        <v>2.46</v>
       </c>
       <c r="K145">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L145">
         <v>0</v>
@@ -37019,10 +37019,10 @@
         <v>0</v>
       </c>
       <c r="P145">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q145">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R145">
         <v>0</v>
@@ -37715,19 +37715,19 @@
         <v>538</v>
       </c>
       <c r="F148">
-        <v>1.32</v>
+        <v>2.8</v>
       </c>
       <c r="G148">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="H148">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="I148">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="J148">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K148">
         <v>4.3</v>
@@ -37745,10 +37745,10 @@
         <v>0</v>
       </c>
       <c r="P148">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q148">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R148">
         <v>0</v>
@@ -37957,22 +37957,22 @@
         <v>539</v>
       </c>
       <c r="F149">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G149">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H149">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="I149">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="J149">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K149">
-        <v>8.199999999999999</v>
+        <v>910</v>
       </c>
       <c r="L149">
         <v>0</v>
@@ -37987,10 +37987,10 @@
         <v>0</v>
       </c>
       <c r="P149">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q149">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R149">
         <v>0</v>
@@ -38199,7 +38199,7 @@
         <v>540</v>
       </c>
       <c r="F150">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="G150">
         <v>1.48</v>
@@ -38208,13 +38208,13 @@
         <v>7.8</v>
       </c>
       <c r="I150">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="J150">
         <v>5.1</v>
       </c>
       <c r="K150">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L150">
         <v>0</v>
@@ -38456,7 +38456,7 @@
         <v>6.4</v>
       </c>
       <c r="K151">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="L151">
         <v>0</v>
@@ -38683,7 +38683,7 @@
         <v>542</v>
       </c>
       <c r="F152">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="G152">
         <v>3.15</v>
@@ -38692,13 +38692,13 @@
         <v>2.22</v>
       </c>
       <c r="I152">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="J152">
         <v>3.85</v>
       </c>
       <c r="K152">
-        <v>6.4</v>
+        <v>100</v>
       </c>
       <c r="L152">
         <v>0</v>
@@ -38713,7 +38713,7 @@
         <v>0</v>
       </c>
       <c r="P152">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q152">
         <v>1.53</v>
@@ -39167,22 +39167,22 @@
         <v>544</v>
       </c>
       <c r="F154">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="G154">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H154">
         <v>4.7</v>
       </c>
       <c r="I154">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J154">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K154">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="L154">
         <v>0</v>
@@ -39197,7 +39197,7 @@
         <v>0</v>
       </c>
       <c r="P154">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q154">
         <v>1.33</v>
@@ -39651,7 +39651,7 @@
         <v>546</v>
       </c>
       <c r="F156">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G156">
         <v>3.6</v>
@@ -39660,13 +39660,13 @@
         <v>2.14</v>
       </c>
       <c r="I156">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J156">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K156">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L156">
         <v>0</v>
@@ -39675,28 +39675,28 @@
         <v>1.06</v>
       </c>
       <c r="N156">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O156">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P156">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q156">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="R156">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S156">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="T156">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U156">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V156">
         <v>0</v>
@@ -39705,13 +39705,13 @@
         <v>0</v>
       </c>
       <c r="X156">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Y156">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z156">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="AA156">
         <v>26</v>
@@ -39732,34 +39732,34 @@
         <v>27</v>
       </c>
       <c r="AG156">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH156">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI156">
         <v>36</v>
       </c>
       <c r="AJ156">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK156">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL156">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM156">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN156">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO156">
         <v>15</v>
       </c>
       <c r="AP156">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ156">
         <v>9.199999999999999</v>
@@ -39786,31 +39786,31 @@
         <v>21</v>
       </c>
       <c r="AY156">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ156">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA156">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BB156">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="BC156">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD156">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BE156">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="BF156">
         <v>23</v>
       </c>
       <c r="BG156">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH156">
         <v>3.6</v>
@@ -39893,22 +39893,22 @@
         <v>547</v>
       </c>
       <c r="F157">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="G157">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="H157">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I157">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J157">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K157">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L157">
         <v>0</v>
@@ -39917,22 +39917,22 @@
         <v>1.03</v>
       </c>
       <c r="N157">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O157">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P157">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q157">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R157">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S157">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T157">
         <v>1.68</v>
@@ -39950,22 +39950,22 @@
         <v>30</v>
       </c>
       <c r="Y157">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z157">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA157">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB157">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC157">
         <v>12.5</v>
       </c>
       <c r="AD157">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE157">
         <v>75</v>
@@ -39983,7 +39983,7 @@
         <v>60</v>
       </c>
       <c r="AJ157">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK157">
         <v>14.5</v>
@@ -39995,19 +39995,19 @@
         <v>75</v>
       </c>
       <c r="AN157">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AO157">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP157">
+        <v>25</v>
+      </c>
+      <c r="AQ157">
         <v>24</v>
       </c>
-      <c r="AQ157">
-        <v>19</v>
-      </c>
       <c r="AR157">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS157">
         <v>14</v>
@@ -40016,7 +40016,7 @@
         <v>11</v>
       </c>
       <c r="AU157">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV157">
         <v>20</v>
@@ -40034,10 +40034,10 @@
         <v>17.5</v>
       </c>
       <c r="BA157">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB157">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BC157">
         <v>13</v>
@@ -40046,10 +40046,10 @@
         <v>21</v>
       </c>
       <c r="BE157">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="BF157">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG157">
         <v>12</v>
@@ -40141,7 +40141,7 @@
         <v>2.08</v>
       </c>
       <c r="H158">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I158">
         <v>4.7</v>
@@ -40150,7 +40150,7 @@
         <v>3.25</v>
       </c>
       <c r="K158">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L158">
         <v>0</v>
@@ -40165,10 +40165,10 @@
         <v>0</v>
       </c>
       <c r="P158">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q158">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R158">
         <v>0</v>
@@ -40377,19 +40377,19 @@
         <v>549</v>
       </c>
       <c r="F159">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G159">
         <v>4.6</v>
       </c>
       <c r="H159">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="I159">
         <v>1.94</v>
       </c>
       <c r="J159">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K159">
         <v>4.3</v>
@@ -40619,22 +40619,22 @@
         <v>550</v>
       </c>
       <c r="F160">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G160">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="H160">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I160">
         <v>3.6</v>
       </c>
       <c r="J160">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K160">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L160">
         <v>0</v>
@@ -41103,13 +41103,13 @@
         <v>552</v>
       </c>
       <c r="F162">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="G162">
         <v>1.93</v>
       </c>
       <c r="H162">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I162">
         <v>5.7</v>
@@ -41118,7 +41118,7 @@
         <v>3.75</v>
       </c>
       <c r="K162">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L162">
         <v>0</v>
@@ -41133,10 +41133,10 @@
         <v>0</v>
       </c>
       <c r="P162">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q162">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R162">
         <v>0</v>
@@ -41145,10 +41145,10 @@
         <v>0</v>
       </c>
       <c r="T162">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U162">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V162">
         <v>0</v>
@@ -41587,10 +41587,10 @@
         <v>554</v>
       </c>
       <c r="F164">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G164">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H164">
         <v>4.8</v>
@@ -41617,7 +41617,7 @@
         <v>0</v>
       </c>
       <c r="P164">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q164">
         <v>1.9</v>
@@ -41650,7 +41650,7 @@
         <v>46</v>
       </c>
       <c r="AA164">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB164">
         <v>8.6</v>
@@ -41659,7 +41659,7 @@
         <v>8.6</v>
       </c>
       <c r="AD164">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE164">
         <v>80</v>
@@ -41689,7 +41689,7 @@
         <v>140</v>
       </c>
       <c r="AN164">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AO164">
         <v>95</v>
@@ -41701,25 +41701,25 @@
         <v>15</v>
       </c>
       <c r="AR164">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS164">
+        <v>8.6</v>
+      </c>
+      <c r="AT164">
         <v>7.8</v>
       </c>
-      <c r="AT164">
+      <c r="AU164">
         <v>7.6</v>
       </c>
-      <c r="AU164">
-        <v>7.8</v>
-      </c>
       <c r="AV164">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW164">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX164">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY164">
         <v>9.199999999999999</v>
@@ -41728,25 +41728,25 @@
         <v>17.5</v>
       </c>
       <c r="BA164">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB164">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC164">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD164">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE164">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BF164">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG164">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH164">
         <v>0</v>
@@ -41829,7 +41829,7 @@
         <v>555</v>
       </c>
       <c r="F165">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G165">
         <v>4.3</v>
@@ -41838,13 +41838,13 @@
         <v>2.16</v>
       </c>
       <c r="I165">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J165">
         <v>3.25</v>
       </c>
       <c r="K165">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L165">
         <v>0</v>
@@ -41898,7 +41898,7 @@
         <v>11.5</v>
       </c>
       <c r="AC165">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD165">
         <v>12</v>
@@ -41946,7 +41946,7 @@
         <v>11</v>
       </c>
       <c r="AS165">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT165">
         <v>10</v>
@@ -41955,40 +41955,40 @@
         <v>6.8</v>
       </c>
       <c r="AV165">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW165">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX165">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY165">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AZ165">
         <v>20</v>
       </c>
       <c r="BA165">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB165">
+        <v>10.5</v>
+      </c>
+      <c r="BC165">
         <v>10</v>
       </c>
-      <c r="BC165">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BD165">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE165">
+        <v>11</v>
+      </c>
+      <c r="BF165">
         <v>10.5</v>
       </c>
-      <c r="BF165">
-        <v>10</v>
-      </c>
       <c r="BG165">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH165">
         <v>0</v>
@@ -42074,7 +42074,7 @@
         <v>1.08</v>
       </c>
       <c r="G166">
-        <v>720</v>
+        <v>160</v>
       </c>
       <c r="H166">
         <v>1.16</v>
@@ -42083,7 +42083,7 @@
         <v>1000</v>
       </c>
       <c r="J166">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K166">
         <v>100</v>
@@ -42101,10 +42101,10 @@
         <v>0</v>
       </c>
       <c r="P166">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q166">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R166">
         <v>0</v>
@@ -42558,10 +42558,10 @@
         <v>4.5</v>
       </c>
       <c r="G168">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H168">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I168">
         <v>1.75</v>
@@ -42570,7 +42570,7 @@
         <v>4.3</v>
       </c>
       <c r="K168">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="L168">
         <v>0</v>
@@ -42803,7 +42803,7 @@
         <v>1.8</v>
       </c>
       <c r="H169">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I169">
         <v>12</v>
@@ -42812,7 +42812,7 @@
         <v>3.6</v>
       </c>
       <c r="K169">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L169">
         <v>0</v>
@@ -42827,7 +42827,7 @@
         <v>0</v>
       </c>
       <c r="P169">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q169">
         <v>1.76</v>
@@ -43039,10 +43039,10 @@
         <v>560</v>
       </c>
       <c r="F170">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G170">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="H170">
         <v>1.73</v>
@@ -43051,10 +43051,10 @@
         <v>2.04</v>
       </c>
       <c r="J170">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K170">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L170">
         <v>0</v>
@@ -43069,7 +43069,7 @@
         <v>0</v>
       </c>
       <c r="P170">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q170">
         <v>1.5</v>
@@ -43281,22 +43281,22 @@
         <v>561</v>
       </c>
       <c r="F171">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G171">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H171">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I171">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J171">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="K171">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="L171">
         <v>1.01</v>
@@ -43305,7 +43305,7 @@
         <v>1.02</v>
       </c>
       <c r="N171">
-        <v>2.64</v>
+        <v>3.7</v>
       </c>
       <c r="O171">
         <v>1.27</v>
@@ -43314,25 +43314,25 @@
         <v>2.02</v>
       </c>
       <c r="Q171">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R171">
         <v>1.38</v>
       </c>
       <c r="S171">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T171">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U171">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V171">
         <v>1.17</v>
       </c>
       <c r="W171">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X171">
         <v>1000</v>
@@ -43347,7 +43347,7 @@
         <v>1000</v>
       </c>
       <c r="AB171">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC171">
         <v>18</v>
@@ -43359,10 +43359,10 @@
         <v>1000</v>
       </c>
       <c r="AF171">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG171">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH171">
         <v>1000</v>
@@ -43383,64 +43383,64 @@
         <v>1000</v>
       </c>
       <c r="AN171">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO171">
         <v>1000</v>
       </c>
       <c r="AP171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AQ171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AR171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AS171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AT171">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AU171">
-        <v>1.05</v>
+        <v>1.32</v>
       </c>
       <c r="AV171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AW171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AX171">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AY171">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AZ171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="BA171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="BB171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="BC171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="BD171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="BE171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="BF171">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="BG171">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="BH171">
         <v>1000</v>
@@ -43526,19 +43526,19 @@
         <v>2.82</v>
       </c>
       <c r="G172">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H172">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I172">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J172">
         <v>3.25</v>
       </c>
       <c r="K172">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="L172">
         <v>0</v>
@@ -43765,7 +43765,7 @@
         <v>563</v>
       </c>
       <c r="F173">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="G173">
         <v>2.52</v>
@@ -43777,10 +43777,10 @@
         <v>4.1</v>
       </c>
       <c r="J173">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K173">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L173">
         <v>0</v>
@@ -44016,7 +44016,7 @@
         <v>1.72</v>
       </c>
       <c r="I174">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="J174">
         <v>4.5</v>
@@ -44049,7 +44049,7 @@
         <v>2.08</v>
       </c>
       <c r="T174">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="U174">
         <v>2.8</v>
@@ -44067,7 +44067,7 @@
         <v>15.5</v>
       </c>
       <c r="Z174">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA174">
         <v>20</v>
@@ -44079,7 +44079,7 @@
         <v>11.5</v>
       </c>
       <c r="AD174">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE174">
         <v>15.5</v>
@@ -44094,10 +44094,10 @@
         <v>16</v>
       </c>
       <c r="AI174">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ174">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AK174">
         <v>46</v>
@@ -44163,7 +44163,7 @@
         <v>28</v>
       </c>
       <c r="BF174">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG174">
         <v>5.6</v>
@@ -44261,7 +44261,7 @@
         <v>2.24</v>
       </c>
       <c r="J175">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K175">
         <v>3.25</v>
@@ -44279,10 +44279,10 @@
         <v>0</v>
       </c>
       <c r="P175">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q175">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="R175">
         <v>0</v>
@@ -45223,7 +45223,7 @@
         <v>1.64</v>
       </c>
       <c r="H179">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I179">
         <v>22</v>
@@ -45232,7 +45232,7 @@
         <v>3.65</v>
       </c>
       <c r="K179">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L179">
         <v>0</v>
@@ -45459,7 +45459,7 @@
         <v>570</v>
       </c>
       <c r="F180">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="G180">
         <v>1.32</v>
@@ -45471,10 +45471,10 @@
         <v>1000</v>
       </c>
       <c r="J180">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="K180">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L180">
         <v>0</v>
@@ -45492,7 +45492,7 @@
         <v>2.86</v>
       </c>
       <c r="Q180">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="R180">
         <v>0</v>
@@ -45701,22 +45701,22 @@
         <v>571</v>
       </c>
       <c r="F181">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="G181">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="H181">
         <v>8</v>
       </c>
       <c r="I181">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J181">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="K181">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="L181">
         <v>0</v>
@@ -45731,7 +45731,7 @@
         <v>0</v>
       </c>
       <c r="P181">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="Q181">
         <v>1.3</v>
@@ -46194,10 +46194,10 @@
         <v>1.79</v>
       </c>
       <c r="I183">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J183">
-        <v>2.92</v>
+        <v>1.61</v>
       </c>
       <c r="K183">
         <v>20</v>
@@ -46218,7 +46218,7 @@
         <v>1.53</v>
       </c>
       <c r="Q183">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="R183">
         <v>0</v>
@@ -46427,16 +46427,16 @@
         <v>574</v>
       </c>
       <c r="F184">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="G184">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H184">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I184">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="J184">
         <v>5.9</v>
@@ -46463,16 +46463,16 @@
         <v>1.4</v>
       </c>
       <c r="R184">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="S184">
         <v>1.99</v>
       </c>
       <c r="T184">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U184">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V184">
         <v>0</v>
@@ -46481,13 +46481,13 @@
         <v>0</v>
       </c>
       <c r="X184">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Y184">
         <v>14.5</v>
       </c>
       <c r="Z184">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA184">
         <v>14.5</v>
@@ -46499,55 +46499,55 @@
         <v>15</v>
       </c>
       <c r="AD184">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE184">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF184">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AG184">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AH184">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI184">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AJ184">
         <v>280</v>
       </c>
       <c r="AK184">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL184">
+        <v>65</v>
+      </c>
+      <c r="AM184">
         <v>70</v>
       </c>
-      <c r="AM184">
-        <v>80</v>
-      </c>
       <c r="AN184">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO184">
         <v>4.1</v>
       </c>
       <c r="AP184">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AQ184">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR184">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS184">
         <v>12.5</v>
       </c>
       <c r="AT184">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AU184">
         <v>13.5</v>
@@ -46559,7 +46559,7 @@
         <v>12</v>
       </c>
       <c r="AX184">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY184">
         <v>25</v>
@@ -46571,22 +46571,22 @@
         <v>20</v>
       </c>
       <c r="BB184">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BC184">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD184">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BE184">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BF184">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BG184">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BH184">
         <v>6.2</v>
@@ -47395,22 +47395,22 @@
         <v>578</v>
       </c>
       <c r="F188">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="G188">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H188">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I188">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J188">
+        <v>3.45</v>
+      </c>
+      <c r="K188">
         <v>3.55</v>
-      </c>
-      <c r="K188">
-        <v>3.65</v>
       </c>
       <c r="L188">
         <v>0</v>
@@ -47419,10 +47419,10 @@
         <v>1.07</v>
       </c>
       <c r="N188">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O188">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P188">
         <v>1.93</v>
@@ -47455,7 +47455,7 @@
         <v>11.5</v>
       </c>
       <c r="Z188">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA188">
         <v>42</v>
@@ -47467,7 +47467,7 @@
         <v>8</v>
       </c>
       <c r="AD188">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE188">
         <v>32</v>
@@ -47503,7 +47503,7 @@
         <v>27</v>
       </c>
       <c r="AP188">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ188">
         <v>10</v>
@@ -47512,16 +47512,16 @@
         <v>16</v>
       </c>
       <c r="AS188">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AT188">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU188">
         <v>7.2</v>
       </c>
       <c r="AV188">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW188">
         <v>19</v>
@@ -47530,19 +47530,19 @@
         <v>16.5</v>
       </c>
       <c r="AY188">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ188">
         <v>15.5</v>
       </c>
       <c r="BA188">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BB188">
         <v>25</v>
       </c>
       <c r="BC188">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="BD188">
         <v>36</v>
@@ -47551,7 +47551,7 @@
         <v>36</v>
       </c>
       <c r="BF188">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG188">
         <v>16.5</v>
@@ -47637,7 +47637,7 @@
         <v>579</v>
       </c>
       <c r="F189">
-        <v>1.53</v>
+        <v>2.82</v>
       </c>
       <c r="G189">
         <v>3.5</v>
@@ -47652,7 +47652,7 @@
         <v>3.2</v>
       </c>
       <c r="K189">
-        <v>910</v>
+        <v>4.1</v>
       </c>
       <c r="L189">
         <v>0</v>
@@ -47882,19 +47882,19 @@
         <v>2.92</v>
       </c>
       <c r="G190">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="H190">
         <v>2.5</v>
       </c>
       <c r="I190">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="J190">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K190">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L190">
         <v>0</v>
@@ -47909,10 +47909,10 @@
         <v>0</v>
       </c>
       <c r="P190">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="Q190">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="R190">
         <v>0</v>
@@ -48121,22 +48121,22 @@
         <v>581</v>
       </c>
       <c r="F191">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="G191">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H191">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="I191">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="J191">
-        <v>1.1</v>
+        <v>2.92</v>
       </c>
       <c r="K191">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L191">
         <v>0</v>
@@ -48151,10 +48151,10 @@
         <v>0</v>
       </c>
       <c r="P191">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="Q191">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="R191">
         <v>0</v>
@@ -48605,10 +48605,10 @@
         <v>583</v>
       </c>
       <c r="F193">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G193">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H193">
         <v>3.8</v>
@@ -48862,7 +48862,7 @@
         <v>1.1</v>
       </c>
       <c r="K194">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="L194">
         <v>0</v>
@@ -49098,7 +49098,7 @@
         <v>2.72</v>
       </c>
       <c r="I195">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J195">
         <v>3.5</v>
@@ -49182,7 +49182,7 @@
         <v>44</v>
       </c>
       <c r="AK195">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL195">
         <v>42</v>
@@ -49206,7 +49206,7 @@
         <v>16.5</v>
       </c>
       <c r="AS195">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT195">
         <v>10.5</v>
@@ -49230,25 +49230,25 @@
         <v>14.5</v>
       </c>
       <c r="BA195">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="BB195">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BC195">
         <v>23</v>
       </c>
       <c r="BD195">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE195">
         <v>8</v>
       </c>
       <c r="BF195">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG195">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH195">
         <v>0</v>
@@ -49331,22 +49331,22 @@
         <v>586</v>
       </c>
       <c r="F196">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G196">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H196">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I196">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J196">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K196">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L196">
         <v>0</v>
@@ -49361,10 +49361,10 @@
         <v>0</v>
       </c>
       <c r="P196">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="Q196">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="R196">
         <v>0</v>
@@ -49588,7 +49588,7 @@
         <v>1.1</v>
       </c>
       <c r="K197">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L197">
         <v>1.01</v>
@@ -49821,7 +49821,7 @@
         <v>2.44</v>
       </c>
       <c r="H198">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I198">
         <v>5.2</v>
@@ -49830,7 +49830,7 @@
         <v>2.88</v>
       </c>
       <c r="K198">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L198">
         <v>0</v>
@@ -49845,10 +49845,10 @@
         <v>0</v>
       </c>
       <c r="P198">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="Q198">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R198">
         <v>0</v>
@@ -50057,16 +50057,16 @@
         <v>589</v>
       </c>
       <c r="F199">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="G199">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H199">
         <v>3.45</v>
       </c>
       <c r="I199">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J199">
         <v>2.94</v>
@@ -50087,10 +50087,10 @@
         <v>0</v>
       </c>
       <c r="P199">
-        <v>1.46</v>
+        <v>1.07</v>
       </c>
       <c r="Q199">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="R199">
         <v>0</v>
